--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486435_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486435_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V. FAVERANI TATSCH</t>
+          <t>S. SVEJCAR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9736</v>
+        <v>4.4703</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7711</v>
+        <v>5.8396</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2025</v>
+        <v>-1.3694</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3055</v>
+        <v>4.0772</v>
       </c>
       <c r="H2" t="n">
-        <v>0.225</v>
+        <v>1.3655</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0805</v>
+        <v>2.7117</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9161</v>
+        <v>5.4703</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6268</v>
+        <v>0.9553</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2893</v>
+        <v>4.515</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6106</v>
+        <v>-1.3931</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4018</v>
+        <v>0.4102</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2088</v>
+        <v>-1.8033</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3926</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R2" t="n">
-        <v>2.3926</v>
+        <v>1.305</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2108</v>
+        <v>-0.7369</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5298</v>
+        <v>0.5444</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.319</v>
+        <v>-1.2813</v>
       </c>
       <c r="V2" t="n">
-        <v>2.0647</v>
+        <v>1.13</v>
       </c>
       <c r="W2" t="n">
-        <v>1.3252</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
-        <v>0.7395</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. SVEJCAR</t>
+          <t>V. FAVERANI TATSCH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0681</v>
+        <v>4.2965</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7149</v>
+        <v>2.9707</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6468</v>
+        <v>1.3258</v>
       </c>
       <c r="G3" t="n">
-        <v>4.0772</v>
+        <v>0.3055</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3655</v>
+        <v>0.225</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7117</v>
+        <v>0.0805</v>
       </c>
       <c r="J3" t="n">
-        <v>5.4703</v>
+        <v>0.9161</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9553</v>
+        <v>0.6268</v>
       </c>
       <c r="L3" t="n">
-        <v>4.515</v>
+        <v>0.2893</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.3931</v>
+        <v>-0.6106</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4102</v>
+        <v>-0.4018</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.8033</v>
+        <v>-0.2088</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.3926</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.305</v>
+        <v>2.3926</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.1391</v>
+        <v>-0.4663</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5804</v>
+        <v>0.7294</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.5587</v>
+        <v>-1.1957</v>
       </c>
       <c r="V3" t="n">
-        <v>1.13</v>
+        <v>2.0647</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13</v>
+        <v>1.3252</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3558</v>
+        <v>1.7279</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1681</v>
+        <v>0.0806</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5239</v>
+        <v>1.6472</v>
       </c>
       <c r="G4" t="n">
         <v>1.1365</v>
@@ -766,13 +766,13 @@
         <v>2.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4778</v>
+        <v>-0.1057</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5876</v>
+        <v>0.8364</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.0654</v>
+        <v>-0.9421</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3904</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. POLYNICE</t>
+          <t>A. DOMENECH FONTANA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2653</v>
+        <v>0.4455</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5071</v>
+        <v>1.8563</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2418</v>
+        <v>-1.4109</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3048</v>
+        <v>-0.4271</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0881</v>
+        <v>1.8519</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3928</v>
+        <v>-2.279</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9766</v>
+        <v>0.766</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2857</v>
+        <v>1.6242</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2622</v>
+        <v>-0.8582</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6718</v>
+        <v>-1.1931</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1976</v>
+        <v>0.2277</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8694</v>
+        <v>-1.4208</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.435</v>
+        <v>1.305</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1751</v>
+        <v>-0.2175</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3956</v>
+        <v>-1.3672</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5756</v>
+        <v>0.1779</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.18</v>
+        <v>-1.5451</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.9347</v>
       </c>
       <c r="W5" t="n">
         <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. DOMENECH FONTANA</t>
+          <t>C. POLYNICE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2593</v>
+        <v>0.044</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7626</v>
+        <v>0.5323</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5033</v>
+        <v>-0.4883</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4271</v>
+        <v>0.3048</v>
       </c>
       <c r="H6" t="n">
-        <v>1.8519</v>
+        <v>-0.0881</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.279</v>
+        <v>0.3928</v>
       </c>
       <c r="J6" t="n">
-        <v>0.766</v>
+        <v>0.9766</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6242</v>
+        <v>-0.2857</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.8582</v>
+        <v>1.2622</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1931</v>
+        <v>-0.6718</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2277</v>
+        <v>0.1976</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.4208</v>
+        <v>-0.8694</v>
       </c>
       <c r="P6" t="n">
-        <v>1.305</v>
+        <v>-0.435</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2175</v>
+        <v>-2.1751</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5534</v>
+        <v>0.1742</v>
       </c>
       <c r="T6" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.6009</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.6376</v>
+        <v>-0.4266</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9347</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. IDEHEN IDEHEN</t>
+          <t>I. RIVERA CARROLL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5264</v>
+        <v>-0.3144</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6442</v>
+        <v>0.2234</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1706</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9671</v>
+        <v>-0.8512999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>2.36</v>
+        <v>1.0189</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3929</v>
+        <v>-1.8702</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2214</v>
+        <v>-0.1387</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5329</v>
+        <v>0.7577</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6885</v>
+        <v>-0.8964</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2543</v>
+        <v>-0.7126</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.2612</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.0814</v>
+        <v>-0.9738</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.9576</v>
+        <v>1.5225</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3926</v>
+        <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
-        <v>0.435</v>
+        <v>2.6101</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6592</v>
+        <v>-0.9857</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6201</v>
+        <v>0.3197</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0392</v>
+        <v>-1.3054</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3904</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. RIVERA CARROLL</t>
+          <t>E. IDEHEN IDEHEN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8428</v>
+        <v>-1.1562</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2741</v>
+        <v>0.4459</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5686</v>
+        <v>-1.6021</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8512999999999999</v>
+        <v>0.9671</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0189</v>
+        <v>2.36</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.8702</v>
+        <v>-1.3929</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1387</v>
+        <v>2.2214</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7577</v>
+        <v>1.5329</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.8964</v>
+        <v>0.6885</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7126</v>
+        <v>-1.2543</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2612</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9738</v>
+        <v>-2.0814</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5225</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0875</v>
+        <v>-2.3926</v>
       </c>
       <c r="R8" t="n">
-        <v>2.6101</v>
+        <v>0.435</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.514</v>
+        <v>0.0294</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1778</v>
+        <v>0.4218</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.3362</v>
+        <v>-0.3924</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.13</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6338</v>
+        <v>-1.4227</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5382</v>
+        <v>0.7185</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.172</v>
+        <v>-2.1412</v>
       </c>
       <c r="G9" t="n">
         <v>0.2397</v>
@@ -1156,13 +1156,13 @@
         <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8735000000000001</v>
+        <v>-0.6624</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0445</v>
+        <v>0.1358</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8290999999999999</v>
+        <v>-0.7982</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5649999999999999</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9262</v>
+        <v>-1.8453</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.796</v>
+        <v>-1.6843</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1302</v>
+        <v>-0.161</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3319</v>
@@ -1234,13 +1234,13 @@
         <v>1.5225</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8341</v>
+        <v>-0.7532</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.113</v>
+        <v>-0.0012</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7211</v>
+        <v>-0.752</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1952</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.9018</v>
+        <v>-5.442</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3208</v>
+        <v>-2.8918</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.581</v>
+        <v>-2.5502</v>
       </c>
       <c r="G11" t="n">
         <v>-4.3605</v>
@@ -1312,13 +1312,13 @@
         <v>0.6525</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6066</v>
+        <v>-1.1467</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.2439</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9336</v>
+        <v>-0.9028</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3698</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.9088999999999992</v>
+        <v>0.8036000000000012</v>
       </c>
       <c r="E12" t="n">
-        <v>6.379100000000001</v>
+        <v>8.091199999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.2879</v>
+        <v>-7.287899999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0600000000000005</v>
+        <v>0.05999999999999961</v>
       </c>
       <c r="H12" t="n">
         <v>8.454799999999999</v>
@@ -1390,13 +1390,13 @@
         <v>15.2254</v>
       </c>
       <c r="S12" t="n">
-        <v>-7.7329</v>
+        <v>-6.020499999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>1.8086</v>
+        <v>3.5212</v>
       </c>
       <c r="U12" t="n">
-        <v>-9.541500000000001</v>
+        <v>-9.541599999999999</v>
       </c>
       <c r="V12" t="n">
         <v>2.4138</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. MC DONNELL</t>
+          <t>R. DIAS MARQUES LISBOA SANTOS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.2164</v>
+        <v>4.4161</v>
       </c>
       <c r="E13" t="n">
-        <v>4.0625</v>
+        <v>4.3359</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1539</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>2.3389</v>
+        <v>4.0507</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2525</v>
+        <v>-1.9951</v>
       </c>
       <c r="I13" t="n">
-        <v>2.5914</v>
+        <v>6.0458</v>
       </c>
       <c r="J13" t="n">
-        <v>3.014</v>
+        <v>5.7738</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2983</v>
+        <v>-0.8633</v>
       </c>
       <c r="L13" t="n">
-        <v>2.7157</v>
+        <v>6.6371</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6751</v>
+        <v>-1.7231</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5508</v>
+        <v>-1.1318</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1243</v>
+        <v>-0.5913</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6525</v>
+        <v>-1.305</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R13" t="n">
-        <v>1.7401</v>
+        <v>1.9576</v>
       </c>
       <c r="S13" t="n">
-        <v>2.1597</v>
+        <v>1.8656</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9408</v>
+        <v>1.6295</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2189</v>
+        <v>0.2361</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.9347</v>
+        <v>-0.1952</v>
       </c>
       <c r="W13" t="n">
         <v>0.1952</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.13</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. GILL</t>
+          <t>S. MC DONNELL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4996</v>
+        <v>3.7463</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2515</v>
+        <v>3.3919</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2481</v>
+        <v>0.3543</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.8276</v>
+        <v>2.3389</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.4842</v>
+        <v>-0.2525</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6566</v>
+        <v>2.5914</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.6219</v>
+        <v>3.014</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.8514</v>
+        <v>0.2983</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2295</v>
+        <v>2.7157</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2057</v>
+        <v>-0.6751</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6328</v>
+        <v>-0.5508</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4271</v>
+        <v>-0.1243</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R14" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9373</v>
+        <v>1.6896</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5933</v>
+        <v>1.2702</v>
       </c>
       <c r="U14" t="n">
-        <v>0.344</v>
+        <v>0.4194</v>
       </c>
       <c r="V14" t="n">
-        <v>2.2599</v>
+        <v>-0.9347</v>
       </c>
       <c r="W14" t="n">
-        <v>2.4552</v>
+        <v>0.1952</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. DIAS MARQUES LISBOA SANTOS</t>
+          <t>R. GILL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.251</v>
+        <v>2.3153</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7771</v>
+        <v>1.1339</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5261</v>
+        <v>1.1814</v>
       </c>
       <c r="G15" t="n">
-        <v>4.0507</v>
+        <v>-0.8276</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.9951</v>
+        <v>-1.4842</v>
       </c>
       <c r="I15" t="n">
-        <v>6.0458</v>
+        <v>0.6566</v>
       </c>
       <c r="J15" t="n">
-        <v>5.7738</v>
+        <v>-0.6219</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.8633</v>
+        <v>-0.8514</v>
       </c>
       <c r="L15" t="n">
-        <v>6.6371</v>
+        <v>0.2295</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7231</v>
+        <v>-0.2057</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1318</v>
+        <v>-0.6328</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5913</v>
+        <v>0.4271</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.305</v>
+        <v>-0.87</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.2626</v>
+        <v>-2.1751</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9576</v>
+        <v>1.305</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7006</v>
+        <v>1.753</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0707</v>
+        <v>1.4757</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3701</v>
+        <v>0.2773</v>
       </c>
       <c r="V15" t="n">
+        <v>2.2599</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.4552</v>
+      </c>
+      <c r="X15" t="n">
         <v>-0.1952</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0.1952</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-0.3904</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0164</v>
+        <v>1.9355</v>
       </c>
       <c r="E16" t="n">
-        <v>4.0107</v>
+        <v>3.4519</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9943</v>
+        <v>-1.5164</v>
       </c>
       <c r="G16" t="n">
         <v>1.1633</v>
@@ -1702,13 +1702,13 @@
         <v>0.435</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9831</v>
+        <v>0.9022</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4456</v>
+        <v>0.8869</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4625</v>
+        <v>0.0153</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5649999999999999</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9303</v>
+        <v>0.8866000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8032</v>
+        <v>0.5797</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1271</v>
+        <v>0.307</v>
       </c>
       <c r="G17" t="n">
         <v>-0.8542999999999999</v>
@@ -1780,13 +1780,13 @@
         <v>0.87</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9146</v>
+        <v>0.8709</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9746</v>
+        <v>0.7511</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.06</v>
+        <v>0.1199</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3165</v>
+        <v>-0.1699</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1868</v>
+        <v>-0.9633</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8703</v>
+        <v>0.7933</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1126</v>
@@ -1858,13 +1858,13 @@
         <v>0.87</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1011</v>
+        <v>1.2477</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6441</v>
+        <v>0.8676</v>
       </c>
       <c r="U18" t="n">
-        <v>0.457</v>
+        <v>0.38</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. IGLESIAS FERNANDEZ</t>
+          <t>K. SMITH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2501</v>
+        <v>-0.8948</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5081</v>
+        <v>-0.2327</v>
       </c>
       <c r="F19" t="n">
-        <v>0.258</v>
+        <v>-0.662</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.6265</v>
+        <v>-0.9536</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4233</v>
+        <v>-1.1345</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2032</v>
+        <v>0.1809</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.3571</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.4719</v>
+        <v>-0.8331</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1147</v>
+        <v>0.9013</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2694</v>
+        <v>-1.0217</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0486</v>
+        <v>-0.3013</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.318</v>
+        <v>-0.7204</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1011</v>
+        <v>0.4933</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1935</v>
+        <v>0.4386</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0924</v>
+        <v>0.0547</v>
       </c>
       <c r="V19" t="n">
-        <v>1.13</v>
+        <v>-1.3045</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>-0.7395</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. FERNANDEZ CARBALLO</t>
+          <t>M. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4799</v>
+        <v>-0.9084</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1195</v>
+        <v>-1.2846</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3604</v>
+        <v>0.3762</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-1.6265</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3285</v>
+        <v>-1.4233</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2335</v>
+        <v>-0.2032</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0365</v>
+        <v>-1.3571</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0365</v>
+        <v>-1.4719</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.1147</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5985</v>
+        <v>-0.2694</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.365</v>
+        <v>0.0486</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2335</v>
+        <v>-0.318</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.87</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0479</v>
+        <v>0.2406</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0205</v>
+        <v>0.2106</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. SMITH</t>
+          <t>S. HUGUET CARRASCO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5524</v>
+        <v>-1.1768</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2327</v>
+        <v>-0.467</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3197</v>
+        <v>-0.7098</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9536</v>
+        <v>-1.3429</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1345</v>
+        <v>-0.2799</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1809</v>
+        <v>-1.063</v>
       </c>
       <c r="J21" t="n">
-        <v>0.06809999999999999</v>
+        <v>-0.7086</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.8331</v>
+        <v>0.0365</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9013</v>
+        <v>-0.7451</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0217</v>
+        <v>-0.6344</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3013</v>
+        <v>-0.3164</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7204</v>
+        <v>-0.318</v>
       </c>
       <c r="P21" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1644</v>
+        <v>0.1661</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4386</v>
+        <v>0.2415</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.603</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.3045</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. HUGUET CARRASCO</t>
+          <t>M. FERNANDEZ CARBALLO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0143</v>
+        <v>-1.3374</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.914</v>
+        <v>-1.0078</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1003</v>
+        <v>-0.3296</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.3429</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2799</v>
+        <v>-0.3285</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.063</v>
+        <v>-0.2335</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7086</v>
+        <v>0.0365</v>
       </c>
       <c r="K22" t="n">
         <v>0.0365</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7451</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6344</v>
+        <v>-0.5985</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3164</v>
+        <v>-0.365</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.318</v>
+        <v>-0.2335</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-0.87</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>0.2175</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6714</v>
+        <v>0.0946</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2055</v>
+        <v>0.0433</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4659</v>
+        <v>0.0514</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0561</v>
+        <v>-1.9168</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2285</v>
+        <v>-2.1167</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8277</v>
+        <v>0.1999</v>
       </c>
       <c r="G23" t="n">
         <v>-1.1881</v>
@@ -2248,13 +2248,13 @@
         <v>1.305</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4538</v>
+        <v>0.6856</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6237</v>
+        <v>0.7355</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0775</v>
+        <v>-0.0499</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5443</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.3354</v>
+        <v>-2.2615</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.4275</v>
+        <v>0.4666</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.9079</v>
+        <v>-2.728</v>
       </c>
       <c r="G24" t="n">
         <v>-0.1454</v>
@@ -2326,13 +2326,13 @@
         <v>0.87</v>
       </c>
       <c r="S24" t="n">
-        <v>0.375</v>
+        <v>1.4489</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2776</v>
+        <v>1.1717</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0974</v>
+        <v>0.2773</v>
       </c>
       <c r="V24" t="n">
         <v>-2.2599</v>
@@ -2359,22 +2359,22 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9089999999999998</v>
+        <v>4.6342</v>
       </c>
       <c r="E25" t="n">
-        <v>7.2879</v>
+        <v>7.287800000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.379</v>
+        <v>-2.6535</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.06009999999999918</v>
+        <v>-0.06009999999999985</v>
       </c>
       <c r="H25" t="n">
         <v>-8.455</v>
       </c>
       <c r="I25" t="n">
-        <v>8.395000000000001</v>
+        <v>8.395</v>
       </c>
       <c r="J25" t="n">
         <v>9.324499999999997</v>
@@ -2389,7 +2389,7 @@
         <v>-9.384599999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>-6.328399999999999</v>
+        <v>-6.3284</v>
       </c>
       <c r="O25" t="n">
         <v>-3.0563</v>
@@ -2404,19 +2404,19 @@
         <v>10.8752</v>
       </c>
       <c r="S25" t="n">
-        <v>7.732799999999998</v>
+        <v>11.4581</v>
       </c>
       <c r="T25" t="n">
-        <v>9.541499999999997</v>
+        <v>9.541600000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.8088</v>
+        <v>1.9167</v>
       </c>
       <c r="V25" t="n">
         <v>-2.4137</v>
       </c>
       <c r="W25" t="n">
-        <v>3.647199999999999</v>
+        <v>3.6472</v>
       </c>
       <c r="X25" t="n">
         <v>-6.061</v>
